--- a/data/WP17/WP17_sachgebiete_fraktionslos_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_fraktionslos_zeitreihe.xlsx
@@ -1852,13 +1852,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{138791AD-64AD-4936-AC1F-09FAB0E6EC1A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA411163-7789-4E6D-88B0-3E0F08BB5780}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B6F229-892E-4411-8FFE-0E5D2DC386D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B23029F4-289C-4A07-B9E7-CF6EF03456C6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20207EFD-1724-4ACF-A168-D3EAEF23256D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD012FF6-B511-4016-9CAA-88C11C472B77}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_fraktionslos_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_fraktionslos_zeitreihe.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve">periode</t>
   </si>
@@ -35,15 +35,15 @@
     <t xml:space="preserve">Anzahl_3</t>
   </si>
   <si>
+    <t xml:space="preserve">Innere Sicherheit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Allgemeinbildende Schulen</t>
   </si>
   <si>
     <t xml:space="preserve">Berufsbildende Schulen</t>
   </si>
   <si>
-    <t xml:space="preserve">Innere Sicherheit</t>
-  </si>
-  <si>
     <t xml:space="preserve">Schulen</t>
   </si>
   <si>
@@ -56,82 +56,85 @@
     <t xml:space="preserve">Außenwirtschaft</t>
   </si>
   <si>
+    <t xml:space="preserve">Polizei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frauen, Männer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinder, Jugendliche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sozialleistungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonstige gesellschaftliche Gruppen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denkmalschutz, Denkmalpflege</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katastrophen- und Zivilschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeitsbedingungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeitsentgelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesundheitsschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landesregierung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berufsausbildung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öffentlicher Dienst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Güterverkehr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alte Menschen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justizverwaltung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abgeordnete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeit und Beschäftigung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bergbau, Bodenschätze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erneuerbare Energien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerichte und Staatsanwaltschaften</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesundheitseinrichtungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychiatrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justizvollzug</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lehrer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polizei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frauen, Männer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinder, Jugendliche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sozialleistungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonstige gesellschaftliche Gruppen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denkmalschutz, Denkmalpflege</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katastrophen- und Zivilschutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wald, Forsten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbeitsbedingungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbeitsentgelt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesundheitsschutz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landesregierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berufsausbildung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentlicher Dienst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Güterverkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alte Menschen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justizverwaltung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abgeordnete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbeit und Beschäftigung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bergbau, Bodenschätze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerichte und Staatsanwaltschaften</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesundheitseinrichtungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psychiatrie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justizvollzug</t>
   </si>
   <si>
     <t xml:space="preserve">Tier, Tierschutz, Tierhaltung</t>
@@ -542,7 +545,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -562,19 +565,19 @@
         <v>43070</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -608,19 +611,19 @@
         <v>43132</v>
       </c>
       <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -634,20 +637,16 @@
         <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6"/>
+      <c r="G6"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -660,13 +659,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
         <v>17</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -683,13 +682,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -706,13 +705,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -723,19 +722,19 @@
         <v>43282</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
         <v>21</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -743,7 +742,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
@@ -757,73 +756,77 @@
       <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="F11"/>
-      <c r="G11"/>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -831,22 +834,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -854,22 +857,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -877,22 +880,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -900,7 +903,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -915,7 +918,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -926,19 +929,19 @@
         <v>43586</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
@@ -949,19 +952,19 @@
         <v>43617</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
         <v>3</v>
@@ -995,19 +998,19 @@
         <v>43709</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1018,26 +1021,30 @@
         <v>43739</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
-      <c r="F23"/>
-      <c r="G23"/>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C24" t="n">
         <v>5</v>
@@ -1049,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
@@ -1060,22 +1067,22 @@
         <v>43800</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1083,7 +1090,7 @@
         <v>43831</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1095,7 +1102,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1106,19 +1113,19 @@
         <v>43862</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -1135,13 +1142,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1152,19 +1159,19 @@
         <v>43922</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -1175,19 +1182,19 @@
         <v>43952</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -1198,13 +1205,13 @@
         <v>43983</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1217,13 +1224,13 @@
         <v>44013</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C32" t="n">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -1242,13 +1249,13 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -1259,7 +1266,7 @@
         <v>44075</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C34" t="n">
         <v>2</v>
@@ -1271,7 +1278,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
@@ -1288,13 +1295,13 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" t="n">
         <v>3</v>
@@ -1311,13 +1318,13 @@
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -1328,19 +1335,19 @@
         <v>44166</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -1351,19 +1358,19 @@
         <v>44197</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -1374,19 +1381,19 @@
         <v>44228</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -1397,19 +1404,19 @@
         <v>44256</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -1420,19 +1427,19 @@
         <v>44287</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C41" t="n">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -1443,19 +1450,19 @@
         <v>44317</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -1466,7 +1473,7 @@
         <v>44348</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" t="n">
         <v>2</v>
@@ -1478,7 +1485,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -1489,19 +1496,19 @@
         <v>44378</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -1512,19 +1519,19 @@
         <v>44409</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C45" t="n">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -1535,19 +1542,19 @@
         <v>44470</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -1558,19 +1565,19 @@
         <v>44501</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -1581,13 +1588,13 @@
         <v>44593</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -1606,13 +1613,13 @@
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -1852,13 +1859,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA411163-7789-4E6D-88B0-3E0F08BB5780}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2C53018-F83F-4DEE-8103-CDC1CF30201B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B23029F4-289C-4A07-B9E7-CF6EF03456C6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC0CA122-E599-4E3A-B03A-EF91B8CA13A0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD012FF6-B511-4016-9CAA-88C11C472B77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{734F2460-75CF-41A9-A388-9F52E160F918}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_fraktionslos_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_fraktionslos_zeitreihe.xlsx
@@ -1859,13 +1859,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2C53018-F83F-4DEE-8103-CDC1CF30201B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981ABFC8-5FD9-48DD-8E86-A75E51988D54}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC0CA122-E599-4E3A-B03A-EF91B8CA13A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8D3AC0-B9A6-4B01-A6CC-60AD495DBD0A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{734F2460-75CF-41A9-A388-9F52E160F918}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E7A6499-5578-48A2-8F1B-2DB580263065}"/>
 </file>